--- a/output/reports/cv_experiment_NaiveBayes_qcut_classification.xlsx
+++ b/output/reports/cv_experiment_NaiveBayes_qcut_classification.xlsx
@@ -491,19 +491,19 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.2046976089477539</v>
+        <v>0.02727746963500977</v>
       </c>
       <c r="E2" t="n">
-        <v>0.6586547164209363</v>
+        <v>0.9788276918439337</v>
       </c>
       <c r="F2" t="n">
-        <v>0.665315429440081</v>
+        <v>0.9805194805194806</v>
       </c>
       <c r="G2" t="n">
-        <v>0.6616285932988146</v>
+        <v>0.9804195804195804</v>
       </c>
       <c r="H2" t="n">
-        <v>0.7263648434311339</v>
+        <v>0.9746309180383507</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -526,23 +526,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.2610921859741211</v>
+        <v>0.04120945930480957</v>
       </c>
       <c r="E3" t="n">
-        <v>0.6590294599111231</v>
+        <v>0.9788074876046238</v>
       </c>
       <c r="F3" t="n">
-        <v>0.665315429440081</v>
+        <v>0.9805194805194806</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6616285932988146</v>
+        <v>0.9804195804195804</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7263653600748099</v>
+        <v>0.9746309180383507</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'var_smoothing': 0.0001, 'priors': None}</t>
+          <t>{'var_smoothing': 1e-11, 'priors': None}</t>
         </is>
       </c>
     </row>
@@ -622,19 +622,19 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.2046976089477539</v>
+        <v>0.02727746963500977</v>
       </c>
       <c r="E2" t="n">
-        <v>0.6586547164209363</v>
+        <v>0.9788276918439337</v>
       </c>
       <c r="F2" t="n">
-        <v>0.665315429440081</v>
+        <v>0.9805194805194806</v>
       </c>
       <c r="G2" t="n">
-        <v>0.6616285932988146</v>
+        <v>0.9804195804195804</v>
       </c>
       <c r="H2" t="n">
-        <v>0.7263648434311339</v>
+        <v>0.9746309180383507</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -657,23 +657,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.2610921859741211</v>
+        <v>0.04120945930480957</v>
       </c>
       <c r="E3" t="n">
-        <v>0.6590294599111231</v>
+        <v>0.9788074876046238</v>
       </c>
       <c r="F3" t="n">
-        <v>0.665315429440081</v>
+        <v>0.9805194805194806</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6616285932988146</v>
+        <v>0.9804195804195804</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7263653600748099</v>
+        <v>0.9746309180383507</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'var_smoothing': 0.0001, 'priors': None}</t>
+          <t>{'var_smoothing': 1e-11, 'priors': None}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_NaiveBayes_qcut_classification.xlsx
+++ b/output/reports/cv_experiment_NaiveBayes_qcut_classification.xlsx
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.02727746963500977</v>
+        <v>0.03673958778381348</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9788276918439337</v>
+        <v>0.5680506174518601</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9805194805194806</v>
+        <v>0.6313559322033898</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9804195804195804</v>
+        <v>0.6092645750229014</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9746309180383507</v>
+        <v>0.8379775926457914</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'var_smoothing': 1e-11, 'priors': None}</t>
+          <t>{'priors': None, 'var_smoothing': 1e-11}</t>
         </is>
       </c>
     </row>
@@ -526,23 +526,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.04120945930480957</v>
+        <v>0.04921722412109375</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9788074876046238</v>
+        <v>0.5665649178081109</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9805194805194806</v>
+        <v>0.6313559322033898</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9804195804195804</v>
+        <v>0.6092645750229014</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9746309180383507</v>
+        <v>0.8379775926457914</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'var_smoothing': 1e-11, 'priors': None}</t>
+          <t>{'priors': None, 'var_smoothing': 1e-11}</t>
         </is>
       </c>
     </row>
@@ -622,23 +622,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.02727746963500977</v>
+        <v>0.03673958778381348</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9788276918439337</v>
+        <v>0.5680506174518601</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9805194805194806</v>
+        <v>0.6313559322033898</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9804195804195804</v>
+        <v>0.6092645750229014</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9746309180383507</v>
+        <v>0.8379775926457914</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'var_smoothing': 1e-11, 'priors': None}</t>
+          <t>{'priors': None, 'var_smoothing': 1e-11}</t>
         </is>
       </c>
     </row>
@@ -657,23 +657,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.04120945930480957</v>
+        <v>0.04921722412109375</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9788074876046238</v>
+        <v>0.5665649178081109</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9805194805194806</v>
+        <v>0.6313559322033898</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9804195804195804</v>
+        <v>0.6092645750229014</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9746309180383507</v>
+        <v>0.8379775926457914</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'var_smoothing': 1e-11, 'priors': None}</t>
+          <t>{'priors': None, 'var_smoothing': 1e-11}</t>
         </is>
       </c>
     </row>
